--- a/triple_sentence_test_with_primes.xlsx
+++ b/triple_sentence_test_with_primes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qubstudentcloud-my.sharepoint.com/personal/40455223_ads_qub_ac_uk/Documents/BioNLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB1D4A5B-F8F6-4D3E-B3D3-79A17F0ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{CB1D4A5B-F8F6-4D3E-B3D3-79A17F0ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5ECC34A-CC69-450F-997E-FADFDA942F05}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38C547DD-FB77-414F-B33F-16A653D8539B}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>Both the Unit and the PF-Unit have the capability to selectively remove various amino acids, especially (AAA) but</t>
   </si>
   <si>
-    <t>Both the Unit and the PF-Unit have the capability to selectively remove various amino acids, especially abdominal aortic aneurysms.</t>
-  </si>
-  <si>
     <t>but</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>was</t>
+  </si>
+  <si>
+    <t>Both the Unit and the PF-Unit have the capability to selectively remove various amino acids, especially abdominal aortic aneurysms but</t>
   </si>
 </sst>
 </file>
@@ -620,10 +620,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -631,28 +631,28 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -660,28 +660,28 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -689,28 +689,28 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -718,31 +718,37 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{eaab77ea-b4a5-49e3-a1e8-d6dd23a1f286}" enabled="0" method="" siteId="{eaab77ea-b4a5-49e3-a1e8-d6dd23a1f286}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/triple_sentence_test_with_primes.xlsx
+++ b/triple_sentence_test_with_primes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qubstudentcloud-my.sharepoint.com/personal/40455223_ads_qub_ac_uk/Documents/BioNLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{CB1D4A5B-F8F6-4D3E-B3D3-79A17F0ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5ECC34A-CC69-450F-997E-FADFDA942F05}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="8_{CB1D4A5B-F8F6-4D3E-B3D3-79A17F0ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73F93933-38F1-46E7-A30C-9C4146BDD4F9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38C547DD-FB77-414F-B33F-16A653D8539B}"/>
+    <workbookView xWindow="41250" yWindow="510" windowWidth="16050" windowHeight="12210" xr2:uid="{38C547DD-FB77-414F-B33F-16A653D8539B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="169">
   <si>
     <t>abbr</t>
   </si>
@@ -182,10 +182,370 @@
     <t>Increase in the (AAA) level was related to the impaired hepatic function and hyperglucagonemia.</t>
   </si>
   <si>
-    <t>was</t>
-  </si>
-  <si>
     <t>Both the Unit and the PF-Unit have the capability to selectively remove various amino acids, especially abdominal aortic aneurysms but</t>
+  </si>
+  <si>
+    <t>ABG</t>
+  </si>
+  <si>
+    <t>INTRODUCTION: Determination of arterial blood gas  values is essential in the evaluation of patients with TCA poisoning.</t>
+  </si>
+  <si>
+    <t>INTRODUCTION: Determination of ( ABG ) values is essential in the evaluation of patients with TCA poisoning.</t>
+  </si>
+  <si>
+    <t>INTRODUCTION: Determination of air bone gap values is essential in the evaluation of patients with TCA poisoning.</t>
+  </si>
+  <si>
+    <t>values</t>
+  </si>
+  <si>
+    <t>MEASUREMENT AND RESULTS: Changes from baseline in arterial blood gas  levels and Kelly score, the rate and causes of NPPV failure, the rate of nosocomial pneumonia, and the 90-day mortality rate were compared.</t>
+  </si>
+  <si>
+    <t>MEASUREMENT AND RESULTS: Changes from baseline in ( ABG ) levels and Kelly score, the rate and causes of NPPV failure, the rate of nosocomial pneumonia, and the 90-day mortality rate were compared.</t>
+  </si>
+  <si>
+    <t>MEASUREMENT AND RESULTS: Changes from baseline in air bone gap levels and Kelly score, the rate and causes of NPPV failure, the rate of nosocomial pneumonia, and the 90-day mortality rate were compared.</t>
+  </si>
+  <si>
+    <t>levels</t>
+  </si>
+  <si>
+    <t>At that time arterial blood gas  analysis revealed a PCO2 of 17.5 kPa (134 mmHg) and pH of 6.9.</t>
+  </si>
+  <si>
+    <t>At that time ( ABG ) analysis revealed a PCO2 of 17.5 kPa (134 mmHg) and pH of 6.9.</t>
+  </si>
+  <si>
+    <t>At that time air bone gap analysis revealed a PCO2 of 17.5 kPa (134 mmHg) and pH of 6.9.</t>
+  </si>
+  <si>
+    <t>analysis</t>
+  </si>
+  <si>
+    <t>Then the arterial blood gas  sample was obtained, an intravenous infusion of methylene blue and vitamin C followed.</t>
+  </si>
+  <si>
+    <t>Then the ( ABG ) sample was obtained, an intravenous infusion of methylene blue and vitamin C followed.</t>
+  </si>
+  <si>
+    <t>Then the air bone gap sample was obtained, an intravenous infusion of methylene blue and vitamin C followed.</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>All subjects also underwent blood pressure, simple spirometric, and arterial blood gas  measurements; cardiac evaluation by radionuclide scanning and CPET; and an overnight polysomnography sleep study before and after nasal CPAP treatment.</t>
+  </si>
+  <si>
+    <t>All subjects also underwent blood pressure, simple spirometric, and ( ABG ) measurements; cardiac evaluation by radionuclide scanning and CPET; and an overnight polysomnography sleep study before and after nasal CPAP treatment.</t>
+  </si>
+  <si>
+    <t>All subjects also underwent blood pressure, simple spirometric, and air bone gap measurements; cardiac evaluation by radionuclide scanning and CPET; and an overnight polysomnography sleep study before and after nasal CPAP treatment.</t>
+  </si>
+  <si>
+    <t>measurements</t>
+  </si>
+  <si>
+    <t>The air-bone gap closure rate did not differ between the 2 groups, except at 4 kHz, where stapedotomy group showed greater closure (P 0.003).</t>
+  </si>
+  <si>
+    <t>The (ABG) closure rate did not differ between the 2 groups, except at 4 kHz, where stapedotomy group showed greater closure (P 0.003).</t>
+  </si>
+  <si>
+    <t>The arterial blood gas closure rate did not differ between the 2 groups, except at 4 kHz, where stapedotomy group showed greater closure (P 0.003).</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>RESULTS: All patients of both groups showed a significant arterial blood gas improvement for all frequencies after surgery ( P&lt;0. 001).</t>
+  </si>
+  <si>
+    <t>RESULTS: All patients of both groups showed a significant (ABG) improvement for all frequencies after surgery ( P&lt;0. 001).</t>
+  </si>
+  <si>
+    <t>RESULTS: All patients of both groups showed a significant air-bone gap improvement for all frequencies after surgery ( P&lt;0. 001).</t>
+  </si>
+  <si>
+    <t>improvement</t>
+  </si>
+  <si>
+    <t>Closure of air-bone gap to within 20 dB was achieved in 6 of 10 patients (60%).</t>
+  </si>
+  <si>
+    <t>Closure of (ABG) to within 20 dB was achieved in 6 of 10 patients (60%).</t>
+  </si>
+  <si>
+    <t>Closure of arterial blood gas to within 20 dB was achieved in 6 of 10 patients (60%).</t>
+  </si>
+  <si>
+    <t>within</t>
+  </si>
+  <si>
+    <t>Average air-bone gap improvement was 13 dB with closure of the ABG to within 20 dB in 57% of cases.</t>
+  </si>
+  <si>
+    <t>Average (ABG) improvement was 13 dB with closure of the ABG to within 20 dB in 57% of cases.</t>
+  </si>
+  <si>
+    <t>Average arterial blood gas improvement was 13 dB with closure of the ABG to within 20 dB in 57% of cases.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: The aim of this study was to evaluate the initial and longer term success of closing the air-bone gap to 20 dB in ossiculoplasty with canal wall down mastoidectomy.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: The aim of this study was to evaluate the initial and longer term success of closing the (ABG) to 20 dB in ossiculoplasty with canal wall down mastoidectomy.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: The aim of this study was to evaluate the initial and longer term success of closing the arterial blood gas to 20 dB in ossiculoplasty with canal wall down mastoidectomy.</t>
+  </si>
+  <si>
+    <t>ossiculoplasty</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>Auditory brainstem response  thresholds were used to evaluate auditory function in mice carrying the Frings Mgr1 allele and were compared with other AGS-susceptible and -resistant mice.</t>
+  </si>
+  <si>
+    <t>( ABR ) thresholds were used to evaluate auditory function in mice carrying the Frings Mgr1 allele and were compared with other AGS-susceptible and -resistant mice.</t>
+  </si>
+  <si>
+    <t>American board of radiology thresholds were used to evaluate auditory function in mice carrying the Frings Mgr1 allele and were compared with other AGS-susceptible and -resistant mice.</t>
+  </si>
+  <si>
+    <t>thresholds</t>
+  </si>
+  <si>
+    <t>The Auditory brainstem response , a measure of neural synchrony, was used to estimate auditory sensitivity in the eastern screech owl (Megascops asio).</t>
+  </si>
+  <si>
+    <t>The ( ABR ), a measure of neural synchrony, was used to estimate auditory sensitivity in the eastern screech owl (Megascops asio).</t>
+  </si>
+  <si>
+    <t>The American board of radiology, a measure of neural synchrony, was used to estimate auditory sensitivity in the eastern screech owl (Megascops asio).</t>
+  </si>
+  <si>
+    <t>measure</t>
+  </si>
+  <si>
+    <t>Most ENT physicians who are not capable of behavioral testing tend to evaluate hearing of infants only from testing Auditory brainstem response and</t>
+  </si>
+  <si>
+    <t>Most ENT physicians who are not capable of behavioral testing tend to evaluate hearing of infants only from testing ( ABR ) and</t>
+  </si>
+  <si>
+    <t>Most ENT physicians who are not capable of behavioral testing tend to evaluate hearing of infants only from testing American board of radiology and</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>Otoacoustic emissions and Auditory brainstem response  suggested the presence of auditory neuropathy in affected individuals.</t>
+  </si>
+  <si>
+    <t>Otoacoustic emissions and ( ABR ) suggested the presence of auditory neuropathy in affected individuals.</t>
+  </si>
+  <si>
+    <t>Otoacoustic emissions and American board of radiology suggested the presence of auditory neuropathy in affected individuals.</t>
+  </si>
+  <si>
+    <t>suggested</t>
+  </si>
+  <si>
+    <t>CONCLUSIONS: Based on the Auditory brainstem response  results obtained in this study, the incidence of deafness in children whose mothers had rubella during pregnancy is high (29.5%), and deafness is profound in most cases (80%).</t>
+  </si>
+  <si>
+    <t>CONCLUSIONS: Based on the  ( ABR ) results obtained in this study, the incidence of deafness in children whose mothers had rubella during pregnancy is high (29.5%), and deafness is profound in most cases (80%).</t>
+  </si>
+  <si>
+    <t>CONCLUSIONS: Based on the American board of radiology results obtained in this study, the incidence of deafness in children whose mothers had rubella during pregnancy is high (29.5%), and deafness is profound in most cases (80%).</t>
+  </si>
+  <si>
+    <t>results</t>
+  </si>
+  <si>
+    <t>ACL</t>
+  </si>
+  <si>
+    <t>Additionally, femoral notch narrowing at the anterior cruciate ligament  insertion site is associated with disease severity, but it is unknown whether ligament deterioration precedes or follows osteophyte formation.</t>
+  </si>
+  <si>
+    <t>Additionally, femoral notch narrowing at the ( ACL ) insertion site is associated with disease severity, but it is unknown whether ligament deterioration precedes or follows osteophyte formation.</t>
+  </si>
+  <si>
+    <t>Additionally, femoral notch narrowing at the anticardiolipin insertion site is associated with disease severity, but it is unknown whether ligament deterioration precedes or follows osteophyte formation.</t>
+  </si>
+  <si>
+    <t>insertion</t>
+  </si>
+  <si>
+    <t>This study reports the initial clinical results of 540 degrees of graft rotation or free tibial bone block to address graft tunnel mismatch in endoscopic anterior cruciate ligament  reconstruction.</t>
+  </si>
+  <si>
+    <t>This study reports the initial clinical results of 540 degrees of graft rotation or free tibial bone block to address graft tunnel mismatch in endoscopic ( ACL ) reconstruction.</t>
+  </si>
+  <si>
+    <t>This study reports the initial clinical results of 540 degrees of graft rotation or free tibial bone block to address graft tunnel mismatch in endoscopic anticardiolipin reconstruction.</t>
+  </si>
+  <si>
+    <t>reconstruction</t>
+  </si>
+  <si>
+    <t>Four patients had anterior cruciate ligament  tear.</t>
+  </si>
+  <si>
+    <t>Four patients had ( ACL ) tear.</t>
+  </si>
+  <si>
+    <t>Four patients had anticardiolipin tear.</t>
+  </si>
+  <si>
+    <t>tear</t>
+  </si>
+  <si>
+    <t>The press-fit fixation technique has become an alternative fixation method in anterior cruciate ligament  reconstruction.</t>
+  </si>
+  <si>
+    <t>The press-fit fixation technique has become an alternative fixation method in ( ACL ) reconstruction.</t>
+  </si>
+  <si>
+    <t>The press-fit fixation technique has become an alternative fixation method in anticardiolipin reconstruction.</t>
+  </si>
+  <si>
+    <t>Primary reconstruction of the anterior cruciate ligament  restores knee stability in up to 95% of patients, but instability can recur.</t>
+  </si>
+  <si>
+    <t>Primary reconstruction of the ( ACL ) restores knee stability in up to 95% of patients, but instability can recur.</t>
+  </si>
+  <si>
+    <t>Primary reconstruction of the anticardiolipin restores knee stability in up to 95% of patients, but instability can recur.</t>
+  </si>
+  <si>
+    <t>restores</t>
+  </si>
+  <si>
+    <t>This article is qualified by the American Board of Radiology in meeting the criteria for self-assessment toward the purpose of fulfilling requirements in the ABR Maintenance of Certification.</t>
+  </si>
+  <si>
+    <t>This article is qualified by the (ABR) in meeting the criteria for self-assessment toward the purpose of fulfilling requirements in the ABR Maintenance of Certification.</t>
+  </si>
+  <si>
+    <t>This article is qualified by the Auditory brainstem response  in meeting the criteria for self-assessment toward the purpose of fulfilling requirements in the ABR Maintenance of Certification.</t>
+  </si>
+  <si>
+    <t>meeting</t>
+  </si>
+  <si>
+    <t>Available rank numbers and rank percentiles for each resident were compared with subsequent performance, as assessed subjectively by 4th-year radiology rotation evaluation forms and retrospective recall of four senior faculty members and objectively by numerical and percentile scores on the written portion of the Auditory brainstem response examinations.</t>
+  </si>
+  <si>
+    <t>Available rank numbers and rank percentiles for each resident were compared with subsequent performance, as assessed subjectively by 4th-year radiology rotation evaluation forms and retrospective recall of four senior faculty members and objectively by numerical and percentile scores on the written portion of the (ABR) examinations.</t>
+  </si>
+  <si>
+    <t>Available rank numbers and rank percentiles for each resident were compared with subsequent performance, as assessed subjectively by 4th-year radiology rotation evaluation forms and retrospective recall of four senior faculty members and objectively by numerical and percentile scores on the written portion of the American Board of Radiology examinations.</t>
+  </si>
+  <si>
+    <t>examinations</t>
+  </si>
+  <si>
+    <t>determined</t>
+  </si>
+  <si>
+    <t>In 1997, the Auditory brainstem response determined to develop a computer-based examination and to create a test center for administration of computer-based examinations</t>
+  </si>
+  <si>
+    <t>In 1997, the (ABR) determined to develop a computer-based examination and to create a test center for administration of computer-based examinations</t>
+  </si>
+  <si>
+    <t>In 1997, the American Board of Radiology determined to develop a computer-based examination and to create a test center for administration of computer-based examinations</t>
+  </si>
+  <si>
+    <t>examination</t>
+  </si>
+  <si>
+    <t>The 1997 survey focused on American Board of Radiology examination preparation, residency curriculum, and socioeconomic issues relevant to graduating radiology residents.</t>
+  </si>
+  <si>
+    <t>The 1997 survey focused on (ABR) examination preparation, residency curriculum, and socioeconomic issues relevant to graduating radiology residents.</t>
+  </si>
+  <si>
+    <t>The 1997 survey focused on Auditory brainstem response examination preparation, residency curriculum, and socioeconomic issues relevant to graduating radiology residents.</t>
+  </si>
+  <si>
+    <t>Residents agreed with recommendations by the American Association of Academic Chief Residents in Radiology concerning proposed changes in the Auditory brainstem response examinations.</t>
+  </si>
+  <si>
+    <t>Residents agreed with recommendations by the American Association of Academic Chief Residents in Radiology concerning proposed changes in the (ABR) examinations.</t>
+  </si>
+  <si>
+    <t>Residents agreed with recommendations by the American Association of Academic Chief Residents in Radiology concerning proposed changes in the American Board of Radiology examinations.</t>
+  </si>
+  <si>
+    <t>previously</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although the presence of anticardiolipin antibodies was previously reported in association with both Graves disease and Hashimoto thyroiditis, I am aware of no previous report of livedo reticularis in patients with Graves disease. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although the presence of (aCL) antibodies was previously reported in association with both Graves disease and Hashimoto thyroiditis, I am aware of no previous report of livedo reticularis in patients with Graves disease. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although the presence of anterior cruciate ligament antibodies was previously reported in association with both Graves disease and Hashimoto thyroiditis, I am aware of no previous report of livedo reticularis in patients with Graves disease. </t>
+  </si>
+  <si>
+    <t>In contrast to lupus circulating anticoagulant and anticardiolipin antibodies, they are usually not found at significant levels in infections.</t>
+  </si>
+  <si>
+    <t>In contrast to lupus circulating anticoagulant and (aCL) antibodies, they are usually not found at significant levels in infections.</t>
+  </si>
+  <si>
+    <t>In contrast to lupus circulating anticoagulant and anterior cruciate ligament antibodies, they are usually not found at significant levels in infections.</t>
+  </si>
+  <si>
+    <t>antibodies</t>
+  </si>
+  <si>
+    <t>We report an infant with anticardiolipin antibodies who presented with erythematous nodular skin lesions and elevated liver enzyme levels.</t>
+  </si>
+  <si>
+    <t>We report an infant with (aCL) antibodies who presented with erythematous nodular skin lesions and elevated liver enzyme levels.</t>
+  </si>
+  <si>
+    <t>We report an infant with anterior cruciate ligament antibodies who presented with erythematous nodular skin lesions and elevated liver enzyme levels.</t>
+  </si>
+  <si>
+    <t>presented</t>
+  </si>
+  <si>
+    <t>BACKGROUND: The association of anticardiolipin antibodies with coronary artery disease has been shown in several studies but remains controversial.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: The association of (aCL) antibodies with coronary artery disease has been shown in several studies but remains controversial.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: The association of anterior cruciate ligament antibodies with coronary artery disease has been shown in several studies but remains controversial.</t>
+  </si>
+  <si>
+    <t>coronary</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: To investigate associations between cerebrovascular risk factors and anticardiolipin immunoreactivity.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: To investigate associations between cerebrovascular risk factors and (aCL) immunoreactivity.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: To investigate associations between cerebrovascular risk factors and anterior cruciate ligament immunoreactivity.</t>
+  </si>
+  <si>
+    <t>immunoreactivity</t>
   </si>
 </sst>
 </file>
@@ -246,6 +606,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -565,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B55822-BF2B-4430-A62C-AA8E2DD5C3AB}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -620,7 +984,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>16</v>
@@ -739,11 +1103,447 @@
         <v>45</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/triple_sentence_test_with_primes.xlsx
+++ b/triple_sentence_test_with_primes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qubstudentcloud-my.sharepoint.com/personal/40455223_ads_qub_ac_uk/Documents/BioNLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="8_{CB1D4A5B-F8F6-4D3E-B3D3-79A17F0ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73F93933-38F1-46E7-A30C-9C4146BDD4F9}"/>
+  <xr:revisionPtr revIDLastSave="371" documentId="8_{CB1D4A5B-F8F6-4D3E-B3D3-79A17F0ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7701F7-3EB1-4339-BA32-C340E399E0F2}"/>
   <bookViews>
-    <workbookView xWindow="41250" yWindow="510" windowWidth="16050" windowHeight="12210" xr2:uid="{38C547DD-FB77-414F-B33F-16A653D8539B}"/>
+    <workbookView xWindow="31320" yWindow="1965" windowWidth="23010" windowHeight="12210" xr2:uid="{38C547DD-FB77-414F-B33F-16A653D8539B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="245">
   <si>
     <t>abbr</t>
   </si>
@@ -546,6 +546,234 @@
   </si>
   <si>
     <t>immunoreactivity</t>
+  </si>
+  <si>
+    <t>ADA</t>
+  </si>
+  <si>
+    <t>The conformational models of the active site of Adenosine deaminase  and its complexes in the basic state with adenosine and 13 isosteric analogues of the aza, deaza, and azadeaza series were constructed.</t>
+  </si>
+  <si>
+    <t>The conformational models of the active site of  ( ADA ) and its complexes in the basic state with adenosine and 13 isosteric analogues of the aza, deaza, and azadeaza series were constructed.</t>
+  </si>
+  <si>
+    <t>The aim of this study was to evaluate the significance of RPT in tuberculosis pleurisy with the patients clinical findings, biochemical and microbiological properties of pleural effusion and with the total Adenosine deaminase  and isoenzymes levels.</t>
+  </si>
+  <si>
+    <t>The aim of this study was to evaluate the significance of RPT in tuberculosis pleurisy with the patients clinical findings, biochemical and microbiological properties of pleural effusion and with the total ( ADA ) and isoenzymes levels.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: The aim of this study was to evaluate saliva's activities of Adenosine deaminase  and 5'-nucleotidase (5'-NT) enzymes and their utility as diagnostic and therapeutic markers in oral and laryngeal cancer.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: The aim of this study was to evaluate saliva's activities of ( ADA ) and 5'-nucleotidase (5'-NT) enzymes and their utility as diagnostic and therapeutic markers in oral and laryngeal cancer.</t>
+  </si>
+  <si>
+    <t>Characterization of Adenosine deaminase  in hemolymph of Biomphalaria glabrata.</t>
+  </si>
+  <si>
+    <t>Characterization of ( ADA ) in hemolymph of Biomphalaria glabrata.</t>
+  </si>
+  <si>
+    <t>Adenosine deaminase  is a key enzyme for the control of extra- and intra-cellular levels of adenosine.</t>
+  </si>
+  <si>
+    <t>( ADA ) is a key enzyme for the control of extra- and intra-cellular levels of adenosine.</t>
+  </si>
+  <si>
+    <t>The conformational models of the active site of American with Disabilities Act and its complexes in the basic state with adenosine and 13 isosteric analogues of the aza, deaza, and azadeaza series were constructed.</t>
+  </si>
+  <si>
+    <t>complexes</t>
+  </si>
+  <si>
+    <t>The aim of this study was to evaluate the significance of RPT in tuberculosis pleurisy with the patients clinical findings, biochemical and microbiological properties of pleural effusion and with the total Americans with Disabilities Act and isoenzymes levels.</t>
+  </si>
+  <si>
+    <t>isoenzymes</t>
+  </si>
+  <si>
+    <t>nucleotidase</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: The aim of this study was to evaluate saliva's activities of Americans with Disabilities Act and 5'-nucleotidase (5'-NT) enzymes and their utility as diagnostic and therapeutic markers in oral and laryngeal cancer.</t>
+  </si>
+  <si>
+    <t>Characterization of Americans with Disabilities Act in hemolymph of Biomphalaria glabrata.</t>
+  </si>
+  <si>
+    <t>hemolymph</t>
+  </si>
+  <si>
+    <t>Americans with Disabilities Act is a key enzyme for the control of extra- and intra-cellular levels of adenosine.</t>
+  </si>
+  <si>
+    <t>enzyme</t>
+  </si>
+  <si>
+    <t>To explore this issue, qualitative archival data were collected and analyzed from 53 (ADA) lawsuits filed against 44 organizations.</t>
+  </si>
+  <si>
+    <t>To explore this issue, qualitative archival data were collected and analyzed from 53 Adenosine deaminase lawsuits filed against 44 organizations.</t>
+  </si>
+  <si>
+    <t>lawsuits</t>
+  </si>
+  <si>
+    <t>To explore this issue, qualitative archival data were collected and analyzed from 53 Americans with Disabilities Act lawsuits filed against 44 organizations.</t>
+  </si>
+  <si>
+    <t>Under the Americans with Disabilities Act, radiologic technology educational programs may not discriminate against qualified disabled individuals who meet admissions criteria.</t>
+  </si>
+  <si>
+    <t>Under the (ADA), radiologic technology educational programs may not discriminate against qualified disabled individuals who meet admissions criteria.</t>
+  </si>
+  <si>
+    <t>Under the Adenosine deaminase, radiologic technology educational programs may not discriminate against qualified disabled individuals who meet admissions criteria.</t>
+  </si>
+  <si>
+    <t>radiologic</t>
+  </si>
+  <si>
+    <t>The Americans with Disabilities Act of 1990 protects people with disabilities from employment discrimination</t>
+  </si>
+  <si>
+    <t>The (ADA) of 1990 protects people with disabilities from employment discrimination</t>
+  </si>
+  <si>
+    <t>The Adenosine deaminase of 1990 protects people with disabilities from employment discrimination</t>
+  </si>
+  <si>
+    <t>protects</t>
+  </si>
+  <si>
+    <t>The plaintiff claims the contractor violated the Americans with Disabilities Act by denying access to his medication.</t>
+  </si>
+  <si>
+    <t>The plaintiff claims the contractor violated the (ADA) by denying access to his medication.</t>
+  </si>
+  <si>
+    <t>The plaintiff claims the contractor violated the Adenosine deaminase by denying access to his medication.</t>
+  </si>
+  <si>
+    <t>denying</t>
+  </si>
+  <si>
+    <t>The company contended that Disanto did not qualify for Americans with Disabilities Act protection because his HIV infection and depression did not substantially limit his ability to work.</t>
+  </si>
+  <si>
+    <t>The company contended that Disanto did not qualify for (ADA) protection because his HIV infection and depression did not substantially limit his ability to work.</t>
+  </si>
+  <si>
+    <t>The company contended that Disanto did not qualify for Adenosine deaminase protection because his HIV infection and depression did not substantially limit his ability to work.</t>
+  </si>
+  <si>
+    <t>protection</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>Phase two showed significant associations between cumulative exposures to thimerosal and the following types of NDs: unspecified developmental delay, tics, Attention Deficit Disorder , language delay, speech delay, and neurodevelopmental delays in general.</t>
+  </si>
+  <si>
+    <t>Phase two showed significant associations between cumulative exposures to thimerosal and the following types of NDs: unspecified developmental delay, tics, ( ADD ), language delay, speech delay, and neurodevelopmental delays in general.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: To review the ways Attention Deficit Disorder  presents in adults in primary care and to suggest treatment approaches.</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: To review the ways ( ADD ) presents in adults in primary care and to suggest treatment approaches.</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>An estimated 7% of children 3-17 years of age had a learning disability, and an estimated 6% of children had ( ADD ) but</t>
+  </si>
+  <si>
+    <t>An estimated 7% of children 3-17 years of age had a learning disability, and an estimated 6% of children had Attention Deficit Disorder but</t>
+  </si>
+  <si>
+    <t>Do neurocognitive measures differentiate Attention Deficit Disorder  with and without hyperactivity?</t>
+  </si>
+  <si>
+    <t>Do neurocognitive measures differentiate  ( ADD ) with and without hyperactivity?</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>presents</t>
+  </si>
+  <si>
+    <t>The purpose of this study was to examine school nurses' knowledge and beliefs about the management of children with Attention Deficit Disorder but</t>
+  </si>
+  <si>
+    <t>The purpose of this study was to examine school nurses' knowledge and beliefs about the management of children with  ( ADD ) but</t>
+  </si>
+  <si>
+    <t>Thioperamide, a standard H(3)-antagonist, did not significantly reduce either seizure ranks or afterdischarge duration but</t>
+  </si>
+  <si>
+    <t>Phase two showed significant associations between cumulative exposures to thimerosal and the following types of NDs: unspecified developmental delay, tics, afterdischarge duration, language delay, speech delay, and neurodevelopmental delays in general.</t>
+  </si>
+  <si>
+    <t>An estimated 7% of children 3-17 years of age had a learning disability, and an estimated 6% of children had afterdischarge duration but</t>
+  </si>
+  <si>
+    <t>Do neurocognitive measures differentiate afterdischarge duration with and without hyperactivity?</t>
+  </si>
+  <si>
+    <t>OBJECTIVE: To review the ways afterdischarge duration presents in adults in primary care and to suggest treatment approaches.</t>
+  </si>
+  <si>
+    <t>The purpose of this study was to examine school nurses' knowledge and beliefs about the management of children with afterdischarge duration but</t>
+  </si>
+  <si>
+    <t>Thioperamide, a standard H(3)-antagonist, did not significantly reduce either seizure ranks or attention deficit disorder but</t>
+  </si>
+  <si>
+    <t>In contrast to the significant differences in number of stimulations to reach the fully kindled state, total (cumulative) afterdischarge duration to reach stage 5 did not significantly differ among strains, substantiating that cumulative AD is the principal factor in the acquisition of kindled seizure.</t>
+  </si>
+  <si>
+    <t>In contrast to the significant differences in number of stimulations to reach the fully kindled state, total (cumulative) (ADD) to reach stage 5 did not significantly differ among strains, substantiating that cumulative AD is the principal factor in the acquisition of kindled seizure</t>
+  </si>
+  <si>
+    <t>In contrast to the significant differences in number of stimulations to reach the fully kindled state, total (cumulative) attention deficit disorder to reach stage 5 did not significantly differ among strains, substantiating that cumulative AD is the principal factor in the acquisition of kindled seizure</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>Changes in afterdischarge duration as well as the expression and progression of behavioral seizures to fully generalized tonic-clonic convulsions (stage 5) were assessed.</t>
+  </si>
+  <si>
+    <t>Changes in (ADD) as well as the expression and progression of behavioral seizures to fully generalized tonic-clonic convulsions (stage 5) were assessed.</t>
+  </si>
+  <si>
+    <t>expression</t>
+  </si>
+  <si>
+    <t>Changes in attention deficit disorder as well as the expression and progression of behavioral seizures to fully generalized tonic-clonic convulsions (stage 5) were assessed.</t>
+  </si>
+  <si>
+    <t>Fifteen hours after the last injection, electrical stimulation was delivered to assess the effects on after discharge threshold and afterdischarge duration therefore</t>
+  </si>
+  <si>
+    <t>Fifteen hours after the last injection, electrical stimulation was delivered to assess the effects on after discharge threshold and (ADD) therefore</t>
+  </si>
+  <si>
+    <t>Fifteen hours after the last injection, electrical stimulation was delivered to assess the effects on after discharge threshold and attention deficit disorder therefore</t>
+  </si>
+  <si>
+    <t>Intra-amygdaloid microinjection of 3-aminopropylarsonate (10 nmol in 0.5 microl injection vehicle) inhibited electrical epileptogenesis by keeping the seizure score at or below stage 1 on the Racine scale, and the attention deficit disorder at or below 19.70 +/- 4.59 s therefore</t>
+  </si>
+  <si>
+    <t>Intra-amygdaloid microinjection of 3-aminopropylarsonate (10 nmol in 0.5 microl injection vehicle) inhibited electrical epileptogenesis by keeping the seizure score at or below stage 1 on the Racine scale, and the (ADD) at or below 19.70 +/- 4.59 s therefore</t>
+  </si>
+  <si>
+    <t>Intra-amygdaloid microinjection of 3-aminopropylarsonate (10 nmol in 0.5 microl injection vehicle) inhibited electrical epileptogenesis by keeping the seizure score at or below stage 1 on the Racine scale, and the afterdischarge duration at or below 19.70 +/- 4.59 s therefore</t>
   </si>
 </sst>
 </file>
@@ -929,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B55822-BF2B-4430-A62C-AA8E2DD5C3AB}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1539,6 +1767,296 @@
       </c>
       <c r="I21" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" t="s">
+        <v>181</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" t="s">
+        <v>183</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I23" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" t="s">
+        <v>184</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" t="s">
+        <v>215</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" t="s">
+        <v>217</v>
+      </c>
+      <c r="C28" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" t="s">
+        <v>220</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>210</v>
+      </c>
+      <c r="B30" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" t="s">
+        <v>229</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
